--- a/segmentation-mask/v1.0.0/segmentation-mask-v1.0.0.xlsx
+++ b/segmentation-mask/v1.0.0/segmentation-mask-v1.0.0.xlsx
@@ -23,34 +23,33 @@
   <commentList>
     <comment ref="A1" authorId="1">
       <text>
-        <t>(Required) Unique HuBMAP or SenNet identifier of the dataset(s) used to generate
-this derived dataset. For example, for a segmentation mask, the parent would be
-the imaging assay that contains the OME TIFF file used. If a derived dataset
-comes from multiple parent datasets then this should be a comma separated list.
-Example: HBM386.ZGKG.235, HBM672.MKPK.442 or SNT232.UBHJ.322, SNT329.ALSK.102</t>
+        <t>The unique identifier from HuBMAP or SenNet for the dataset(s) used to generate
+this derived dataset. For example, in the case of a segmentation mask, the
+parent dataset would be the imaging assay containing the OME TIFF file utilized.
+If the derived dataset originates from multiple parent datasets, list them
+separated by commas. Example: HBM386.ZGKG.235</t>
       </text>
     </comment>
     <comment ref="B1" authorId="1">
       <text>
-        <t>An internal field labs can use it to add whatever ID(s) they want or need for
-dataset validation and tracking. This could be a single ID (e.g.,
-"Visium_9OLC_A4_S1") or a delimited list of IDs (e.g., “9OL; 9OLC.A2;
-Visium_9OLC_A4_S1”). This field will not be accessible to anyone outside of the
-consortium and no effort will be made to check if IDs provided by one data
-provider are also used by another.</t>
+        <t>An identifier assigned by the data provider to reference an external metadata
+record for the dataset. The external record may be maintained independently and
+can support dataset traceability and provenance tracking. Leave this field empty
+if no such identifier exists.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="1">
       <text>
-        <t>(Required) DOI for the protocols.io page that describes the analysis performed
-when generating this dataset. For example, for an analysis of a sequencing
-dataset, the protocol should explain the pipeline run, reference libraries used,
-and URLs for critical programs.</t>
+        <t>The DOI for the protocols.io page that outlines the analysis conducted to
+generate this dataset. For instance, in the analysis of a sequencing dataset,
+the protocol should detail the pipeline executed, reference libraries utilized,
+and URLs for the tool programs.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="1">
       <text>
-        <t>(Required) The specific type of analysis being executed.</t>
+        <t>The specific type of analysis being conducted to generate the derived dataset.
+Example: Segmentation Mask</t>
       </text>
     </comment>
     <comment ref="E1" authorId="1">
@@ -69,33 +68,32 @@
     </comment>
     <comment ref="F1" authorId="1">
       <text>
-        <t>(Required) The path to the file with the ORCID IDs for all contributors of this
-dataset (e.g., "./extras/contributors.tsv" or "./contributors.tsv"). This is an
-internal metadata field that is just used for ingest.</t>
+        <t>The name of the file containing the ORCID IDs for all contributors to this
+dataset. Example: ./contributors.csv</t>
       </text>
     </comment>
     <comment ref="G1" authorId="1">
       <text>
-        <t>(Required) The top level directory containing the raw and/or processed data. For
-a single dataset upload this might be "." where as for a data upload containing
-multiple datasets, this would be the directory name for the respective dataset.
-For instance, if the data is within a directory called "TEST001-RK" use syntax
-"./TEST001-RK" for this field. If there are multiple directory levels, use the
-format "./TEST001-RK/Run1/Pass2" in which "Pass2" is the subdirectory where the
-single dataset's data is stored. This is an internal metadata field that is just
-used for ingest.</t>
+        <t>The top-level directory containing the raw and/or processed data. For a single
+dataset upload, this might be represented as ".", whereas for a data upload
+containing multiple datasets, this would be the directory name for the
+respective dataset. For example, if the data is within a directory named
+"TEST001-RK", use the syntax "./TEST001-RK" for this field. If there are
+multiple directory levels, use the format "./TEST001-RK/Run1/Pass2", where
+"Pass2" is the subdirectory where the single dataset's data is stored. This is
+an internal metadata field used solely for data ingestion. Example: ./TEST001-RK</t>
       </text>
     </comment>
     <comment ref="H1" authorId="1">
       <text>
-        <t>(Required) This field specifies if the dataset includes cell type annotations
-("Yes" or "No").</t>
+        <t>Indicates whether cell type annotations are included in the dataset. Answer with
+"Yes" or "No" value. Example: Yes</t>
       </text>
     </comment>
     <comment ref="I1" authorId="1">
       <text>
-        <t>(Required) The string that serves as the definitive identifier for the metadata
-schema version and is readily interpretable by computers for data validation and
+        <t>The unique string identifier for the metadata specification version, which is
+easily interpretable by computers for purposes of data validation and
 processing. Example: 22bc762a-5020-419d-b170-24253ed9e8d9</t>
       </text>
     </comment>
@@ -104,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>parent_dataset_id</t>
   </si>
@@ -124,6 +122,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000314</t>
   </si>
   <si>
+    <t>Object x Analyte</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000403</t>
+  </si>
+  <si>
     <t>program_url</t>
   </si>
   <si>
@@ -160,7 +164,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2024-08-07T09:56:44-07:00</t>
+    <t>2026-10-21T13:38:20-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -269,33 +273,30 @@
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
-      <c r="D2" t="s" s="5">
-        <v>4</v>
-      </c>
       <c r="I2" t="s" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" sqref="D2:D1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'derived_dataset_type'!$A$1:$A$1</formula1>
+      <formula1>'derived_dataset_type'!$A$1:$A$2</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="H2:H1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'is_cell_type_annotation_include'!$A$1:$A$2</formula1>
@@ -309,7 +310,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -318,6 +319,14 @@
       </c>
       <c r="B1" t="s" s="0">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -332,12 +341,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -358,16 +367,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
@@ -375,13 +384,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
